--- a/content/Photo_Studio_TPV_Biblioteca_de_Prompts.xlsx
+++ b/content/Photo_Studio_TPV_Biblioteca_de_Prompts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Datas Comemorativas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evergreen'!$A$1:$L$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evergreen'!$A$1:$K$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Datas Comemorativas'!$A$1:$L$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J24"/>
+  <dimension ref="B2:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -489,14 +489,14 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Photo Studio TPV — Biblioteca de Prompts (Fotos-Mestre)</t>
+          <t>Photo Studio TPV — Biblioteca de Prompts (v2)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Base para gerar as imagens de referência do catálogo no Gemini</t>
+          <t>Reescrita com base em prompts reais do concorrente (Studio Pablita)</t>
         </is>
       </c>
     </row>
@@ -506,66 +506,66 @@
     <row r="6" ht="16" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>COMO USAR ESTA PLANILHA</t>
+          <t>O QUE MUDOU NA V2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>1. Abra a aba 'Evergreen' (situações permanentes) ou 'Datas Comemorativas'.</t>
+          <t>Os prompts foram reescritos incorporando técnicas reais observadas em prompts do concorrente: física de equilíbrio/gravidade das peças, vocabulário de câmera e iluminação de estúdio, proteções contra erros clássicos de geração por IA (duplicação, flutuação, correntes/curvas simétricas demais, reinterpretação de acabamento ou escala), composição sem rosto nas fotos humanizadas, sombra diagonal como assinatura visual, e auto-checagem final antes de considerar a imagem pronta.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>2. Escolha uma linha. Copie o texto da coluna 'Prompt Mestre'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>3. Se o prompt tiver o marcador [PERFIL], substitua por uma das opções da coluna 'Perfis Sugeridos' (gere uma foto-mestre para cada perfil, se quiser variedade de representação).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+      <c r="B8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>COMO USAR ESTA PLANILHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4. Cole o prompt no Gemini, anexando a foto de uma peça genérica do catálogo da TPV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>1. Abra a aba 'Evergreen' ou 'Datas Comemorativas'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>5. Gere a imagem. Se ficar boa, salve o arquivo com o nome sugerido na coluna 'Nome de Referência' e cole o link/caminho na coluna 'Link da Imagem Gerada'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
+          <t>2. Copie o texto da coluna 'Prompt Mestre' de uma linha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>6. Marque a coluna 'Status' como 'Gerado' ou 'Aprovado'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>POR QUE GERAR AS REFERÊNCIAS NO GEMINI (E NÃO EM BANCO DE IMAGENS)</t>
+          <t>3. Se o prompt tiver [PERFIL], substitua por uma das opções de 'Perfis Sugeridos'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>4. Cole no Gemini (ou ChatGPT), anexando a foto de uma peça genérica do catálogo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>5. Gere a imagem. Se ficou boa, salve com o nome de 'Nome de Referência'.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>O catálogo do Photo Studio TPV mostra à cliente um preview do estilo. Gerando o preview com o MESMO motor (Gemini) que fará a geração final da cliente, garantimos que o resultado prometido é sempre o resultado entregue (WYSIWYG) — evita frustração e evita usar imagens de terceiros sem direito de uso.</t>
+          <t>6. Suba no Supabase e marque a linha como 'aprovado' (ver README do projeto).</t>
         </is>
       </c>
     </row>
@@ -575,77 +575,41 @@
     <row r="17" ht="16" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ESTRUTURA DO PROMPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+          <t>LEGENDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Todo prompt tem 3 blocos fixos: (1) instrução de fidelidade da peça — nunca remover, é o diferencial de venda da ferramenta; (2) descrição da cena/pose; (3) especificação fotográfica técnica (iluminação, fundo, proporção).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>LEGENDA DAS COLUNAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Tem Modelo? — indica se a pose usa parte do corpo ou modelo completo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Perfis Sugeridos — variações de gênero/idade/tom de pele para rodar o mesmo prompt mais de uma vez, ampliando a diversidade de referências no catálogo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Proporção — formato de imagem sugerido para exportação (compatível com uso em e-commerce/Instagram).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Status — controle de produção: A gerar / Gerado / Aprovado / Reprovar (refazer).</t>
+          <t>Tem Modelo? — indica se a pose usa parte do corpo (sempre sem rosto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Perfis Sugeridos — variações de gênero/idade/tom de pele para gerar mais de uma vez o mesmo prompt, ampliando a diversidade de referências no catálogo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="15">
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B7:J7"/>
     <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="B10:J10"/>
     <mergeCell ref="B14:J14"/>
     <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="B18:J18"/>
     <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B12:J12"/>
     <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="B9:J9"/>
     <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B20:J20"/>
     <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -657,21 +621,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -702,41 +665,36 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>Cenário/Arranjo Base</t>
+          <t>Nome de Referência</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>Nome de Referência</t>
+          <t>Prompt Mestre</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>Prompt Mestre</t>
+          <t>Proporção</t>
         </is>
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>Proporção</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Link da Imagem Gerada</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
-          <t>Link da Imagem Gerada</t>
-        </is>
-      </c>
-      <c r="L1" s="5" t="inlineStr">
-        <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
@@ -758,35 +716,31 @@
       <c r="E2" s="6" t="inlineStr"/>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Um par de brincos posicionado lado a lado, simetricamente</t>
+          <t>brinco_still-branco-packshot</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>brinco_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr"/>
       <c r="K2" s="6" t="inlineStr"/>
-      <c r="L2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3" ht="90" customHeight="1">
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
@@ -802,7 +756,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -812,35 +766,31 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>a orelha e lateral do rosto</t>
+          <t>brinco_still-humanizado</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>brinco_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente, com a orelha e lateral do rosto como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com a orelha e lateral do rosto levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr"/>
       <c r="K3" s="6" t="inlineStr"/>
-      <c r="L3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="90" customHeight="1">
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
@@ -862,35 +812,31 @@
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Um par de brincos posicionado lado a lado, simetricamente</t>
+          <t>brinco_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>brinco_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="6" t="inlineStr"/>
-      <c r="L4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="90" customHeight="1">
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
@@ -912,35 +858,31 @@
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Um par de brincos posicionado lado a lado, simetricamente</t>
+          <t>brinco_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>brinco_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="90" customHeight="1">
+    </row>
+    <row r="6" ht="130" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
@@ -956,7 +898,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -966,35 +908,31 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>a orelha e lateral do rosto</t>
+          <t>brinco_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>brinco_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="90" customHeight="1">
+    </row>
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
@@ -1016,35 +954,31 @@
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total</t>
+          <t>colar_still-branco-packshot</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>colar_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+    </row>
+    <row r="8" ht="130" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
@@ -1060,7 +994,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1070,35 +1004,31 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>o colo e o pescoço</t>
+          <t>colar_still-humanizado</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>colar_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total, com o colo e o pescoço como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o colo e o pescoço levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
       <c r="K8" s="6" t="inlineStr"/>
-      <c r="L8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+    </row>
+    <row r="9" ht="130" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
@@ -1120,35 +1050,31 @@
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total</t>
+          <t>colar_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>colar_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr"/>
-      <c r="L9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10" ht="90" customHeight="1">
+    </row>
+    <row r="10" ht="130" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
@@ -1170,35 +1096,31 @@
       <c r="E10" s="6" t="inlineStr"/>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total</t>
+          <t>colar_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>colar_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
-      <c r="L10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
+    </row>
+    <row r="11" ht="130" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
@@ -1214,7 +1136,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1224,35 +1146,31 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>o colo e o pescoço</t>
+          <t>colar_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>colar_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
       <c r="K11" s="6" t="inlineStr"/>
-      <c r="L11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
+    </row>
+    <row r="12" ht="130" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
@@ -1274,35 +1192,31 @@
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Choker disposta em curva, simulando o formato do pescoço</t>
+          <t>choker-gargantilha_still-branco-packshot</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>choker-gargantilha_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Choker disposta em curva, simulando o formato do pescoço.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
       <c r="K12" s="6" t="inlineStr"/>
-      <c r="L12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
+    </row>
+    <row r="13" ht="130" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
@@ -1318,7 +1232,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1328,35 +1242,31 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>o pescoço</t>
+          <t>choker-gargantilha_still-humanizado</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>choker-gargantilha_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pescoço, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pescoço — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Choker disposta em curva, simulando o formato do pescoço, com o pescoço como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o pescoço levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="6" t="inlineStr"/>
-      <c r="L13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
+    </row>
+    <row r="14" ht="130" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
@@ -1378,35 +1288,31 @@
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Choker disposta em curva, simulando o formato do pescoço</t>
+          <t>choker-gargantilha_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>choker-gargantilha_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Choker disposta em curva, simulando o formato do pescoço.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
+    </row>
+    <row r="15" ht="130" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
@@ -1428,35 +1334,31 @@
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Choker disposta em curva, simulando o formato do pescoço</t>
+          <t>choker-gargantilha_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>choker-gargantilha_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Choker disposta em curva, simulando o formato do pescoço, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
+    </row>
+    <row r="16" ht="130" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
@@ -1472,7 +1374,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1482,35 +1384,31 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>o pescoço</t>
+          <t>choker-gargantilha_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>choker-gargantilha_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pescoço, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pescoço usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pescoço.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+    </row>
+    <row r="17" ht="130" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
@@ -1532,35 +1430,31 @@
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Colar longo disposto em curvas suaves, mostrando todo o comprimento</t>
+          <t>colar-longo_still-branco-packshot</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>colar-longo_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar longo disposto em curvas suaves, mostrando todo o comprimento.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
+    </row>
+    <row r="18" ht="130" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>17</v>
       </c>
@@ -1576,7 +1470,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1586,35 +1480,31 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>o colo e o decote</t>
+          <t>colar-longo_still-humanizado</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>colar-longo_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo e o decote, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo e o decote — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar longo disposto em curvas suaves, mostrando todo o comprimento, com o colo e o decote como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o colo e o decote levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
       <c r="K18" s="6" t="inlineStr"/>
-      <c r="L18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
+    </row>
+    <row r="19" ht="130" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
@@ -1636,35 +1526,31 @@
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Colar longo disposto em curvas suaves, mostrando todo o comprimento</t>
+          <t>colar-longo_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>colar-longo_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar longo disposto em curvas suaves, mostrando todo o comprimento.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr"/>
-      <c r="L19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+    </row>
+    <row r="20" ht="130" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>19</v>
       </c>
@@ -1686,35 +1572,31 @@
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Colar longo disposto em curvas suaves, mostrando todo o comprimento</t>
+          <t>colar-longo_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>colar-longo_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar longo disposto em curvas suaves, mostrando todo o comprimento, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr"/>
-      <c r="L20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+    </row>
+    <row r="21" ht="130" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
@@ -1730,7 +1612,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1740,35 +1622,31 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>o colo e o decote</t>
+          <t>colar-longo_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>colar-longo_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo e o decote, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo e o decote usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o decote.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
+    </row>
+    <row r="22" ht="130" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>21</v>
       </c>
@@ -1790,35 +1668,31 @@
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Pingente centralizado com a corrente disposta de forma orgânica ao redor</t>
+          <t>pingente_still-branco-packshot</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>pingente_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pingente centralizado com a corrente disposta de forma orgânica ao redor.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
+    </row>
+    <row r="23" ht="130" customHeight="1">
       <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
@@ -1834,7 +1708,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1844,35 +1718,31 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>o colo, próximo ao centro do peito</t>
+          <t>pingente_still-humanizado</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>pingente_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, próximo ao centro do peito, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, próximo ao centro do peito — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pingente centralizado com a corrente disposta de forma orgânica ao redor, com o colo, próximo ao centro do peito como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o colo, próximo ao centro do peito levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
+    </row>
+    <row r="24" ht="130" customHeight="1">
       <c r="A24" s="6" t="n">
         <v>23</v>
       </c>
@@ -1894,35 +1764,31 @@
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Pingente centralizado com a corrente disposta de forma orgânica ao redor</t>
+          <t>pingente_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>pingente_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pingente centralizado com a corrente disposta de forma orgânica ao redor.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr"/>
       <c r="K24" s="6" t="inlineStr"/>
-      <c r="L24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
+    </row>
+    <row r="25" ht="130" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
@@ -1944,35 +1810,31 @@
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Pingente centralizado com a corrente disposta de forma orgânica ao redor</t>
+          <t>pingente_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>pingente_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pingente centralizado com a corrente disposta de forma orgânica ao redor, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
+    </row>
+    <row r="26" ht="130" customHeight="1">
       <c r="A26" s="6" t="n">
         <v>25</v>
       </c>
@@ -1988,7 +1850,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1998,35 +1860,31 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>o colo, próximo ao centro do peito</t>
+          <t>pingente_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>pingente_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, próximo ao centro do peito, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo, próximo ao centro do peito usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo, próximo ao centro do peito.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr"/>
       <c r="K26" s="6" t="inlineStr"/>
-      <c r="L26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
+    </row>
+    <row r="27" ht="130" customHeight="1">
       <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
@@ -2048,35 +1906,31 @@
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Corrente disposta em linha reta ou levemente curva, evidenciando o elo</t>
+          <t>corrente-masculina_still-branco-packshot</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>corrente-masculina_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Corrente disposta em linha reta ou levemente curva, evidenciando o elo.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr"/>
-      <c r="L27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
+    </row>
+    <row r="28" ht="130" customHeight="1">
       <c r="A28" s="6" t="n">
         <v>27</v>
       </c>
@@ -2092,7 +1946,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -2102,35 +1956,31 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>o pescoço, estilo masculino</t>
+          <t>corrente-masculina_still-humanizado</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>corrente-masculina_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o peito e a base do pescoço, com estilo masculino, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o peito e a base do pescoço, com estilo masculino — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Corrente disposta em linha reta ou levemente curva, evidenciando o elo, com o pescoço, estilo masculino como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o pescoço, estilo masculino levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr"/>
       <c r="K28" s="6" t="inlineStr"/>
-      <c r="L28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
+    </row>
+    <row r="29" ht="130" customHeight="1">
       <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
@@ -2152,35 +2002,31 @@
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Corrente disposta em linha reta ou levemente curva, evidenciando o elo</t>
+          <t>corrente-masculina_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>corrente-masculina_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Corrente disposta em linha reta ou levemente curva, evidenciando o elo.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr"/>
-      <c r="L29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
+    </row>
+    <row r="30" ht="130" customHeight="1">
       <c r="A30" s="6" t="n">
         <v>29</v>
       </c>
@@ -2202,35 +2048,31 @@
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Corrente disposta em linha reta ou levemente curva, evidenciando o elo</t>
+          <t>corrente-masculina_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>corrente-masculina_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Corrente disposta em linha reta ou levemente curva, evidenciando o elo, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr"/>
       <c r="K30" s="6" t="inlineStr"/>
-      <c r="L30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
+    </row>
+    <row r="31" ht="130" customHeight="1">
       <c r="A31" s="6" t="n">
         <v>30</v>
       </c>
@@ -2246,7 +2088,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -2256,35 +2098,31 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>o pescoço, estilo masculino</t>
+          <t>corrente-masculina_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>corrente-masculina_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o peito e a base do pescoço, com estilo masculino, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o peito e a base do pescoço, com estilo masculino usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pescoço, estilo masculino.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="6" t="inlineStr"/>
-      <c r="L31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
+    </row>
+    <row r="32" ht="130" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>31</v>
       </c>
@@ -2306,35 +2144,31 @@
       <c r="E32" s="6" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível</t>
+          <t>pulseira_still-branco-packshot</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>pulseira_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr"/>
       <c r="K32" s="6" t="inlineStr"/>
-      <c r="L32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
+    </row>
+    <row r="33" ht="130" customHeight="1">
       <c r="A33" s="6" t="n">
         <v>32</v>
       </c>
@@ -2350,7 +2184,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -2360,35 +2194,31 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>o pulso</t>
+          <t>pulseira_still-humanizado</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>pulseira_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível, com o pulso como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o pulso levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr"/>
       <c r="K33" s="6" t="inlineStr"/>
-      <c r="L33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
+    </row>
+    <row r="34" ht="130" customHeight="1">
       <c r="A34" s="6" t="n">
         <v>33</v>
       </c>
@@ -2410,35 +2240,31 @@
       <c r="E34" s="6" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível</t>
+          <t>pulseira_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>pulseira_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr"/>
       <c r="K34" s="6" t="inlineStr"/>
-      <c r="L34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
+    </row>
+    <row r="35" ht="130" customHeight="1">
       <c r="A35" s="6" t="n">
         <v>34</v>
       </c>
@@ -2460,35 +2286,31 @@
       <c r="E35" s="6" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível</t>
+          <t>pulseira_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>pulseira_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
       <c r="K35" s="6" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
+    </row>
+    <row r="36" ht="130" customHeight="1">
       <c r="A36" s="6" t="n">
         <v>35</v>
       </c>
@@ -2504,7 +2326,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -2514,35 +2336,31 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>o pulso</t>
+          <t>pulseira_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>pulseira_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr"/>
       <c r="K36" s="6" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
+    </row>
+    <row r="37" ht="130" customHeight="1">
       <c r="A37" s="6" t="n">
         <v>36</v>
       </c>
@@ -2564,35 +2382,31 @@
       <c r="E37" s="6" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Bracelete apoiado na vertical, mostrando sua estrutura rígida e o formato circular</t>
+          <t>bracelete-bangle_still-branco-packshot</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>bracelete-bangle_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Bracelete apoiado na vertical, mostrando sua estrutura rígida e o formato circular.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr"/>
       <c r="K37" s="6" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
+    </row>
+    <row r="38" ht="130" customHeight="1">
       <c r="A38" s="6" t="n">
         <v>37</v>
       </c>
@@ -2608,7 +2422,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2618,35 +2432,31 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>o pulso e o antebraço</t>
+          <t>bracelete-bangle_still-humanizado</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>bracelete-bangle_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso e o antebraço, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso e o antebraço — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Bracelete apoiado na vertical, mostrando sua estrutura rígida e o formato circular, com o pulso e o antebraço como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o pulso e o antebraço levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr"/>
       <c r="K38" s="6" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
+    </row>
+    <row r="39" ht="130" customHeight="1">
       <c r="A39" s="6" t="n">
         <v>38</v>
       </c>
@@ -2668,35 +2478,31 @@
       <c r="E39" s="6" t="inlineStr"/>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Bracelete apoiado na vertical, mostrando sua estrutura rígida e o formato circular</t>
+          <t>bracelete-bangle_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>bracelete-bangle_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Bracelete apoiado na vertical, mostrando sua estrutura rígida e o formato circular.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
+    </row>
+    <row r="40" ht="130" customHeight="1">
       <c r="A40" s="6" t="n">
         <v>39</v>
       </c>
@@ -2718,35 +2524,31 @@
       <c r="E40" s="6" t="inlineStr"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Bracelete apoiado na vertical, mostrando sua estrutura rígida e o formato circular</t>
+          <t>bracelete-bangle_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>bracelete-bangle_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Bracelete apoiado na vertical, mostrando sua estrutura rígida e o formato circular, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr"/>
       <c r="K40" s="6" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
+    </row>
+    <row r="41" ht="130" customHeight="1">
       <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
@@ -2762,7 +2564,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -2772,35 +2574,31 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>o pulso e o antebraço</t>
+          <t>bracelete-bangle_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>bracelete-bangle_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso e o antebraço, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso e o antebraço usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso e o antebraço.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr"/>
       <c r="K41" s="6" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
+    </row>
+    <row r="42" ht="130" customHeight="1">
       <c r="A42" s="6" t="n">
         <v>41</v>
       </c>
@@ -2822,35 +2620,31 @@
       <c r="E42" s="6" t="inlineStr"/>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal</t>
+          <t>anel_still-branco-packshot</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>anel_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr"/>
       <c r="K42" s="6" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
+    </row>
+    <row r="43" ht="130" customHeight="1">
       <c r="A43" s="6" t="n">
         <v>42</v>
       </c>
@@ -2866,7 +2660,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2876,35 +2670,31 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>a mão e os dedos</t>
+          <t>anel_still-humanizado</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>anel_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal, com a mão e os dedos como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com a mão e os dedos levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr"/>
       <c r="K43" s="6" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
+    </row>
+    <row r="44" ht="130" customHeight="1">
       <c r="A44" s="6" t="n">
         <v>43</v>
       </c>
@@ -2926,35 +2716,31 @@
       <c r="E44" s="6" t="inlineStr"/>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal</t>
+          <t>anel_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>anel_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr"/>
       <c r="K44" s="6" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
+    </row>
+    <row r="45" ht="130" customHeight="1">
       <c r="A45" s="6" t="n">
         <v>44</v>
       </c>
@@ -2976,35 +2762,31 @@
       <c r="E45" s="6" t="inlineStr"/>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal</t>
+          <t>anel_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>anel_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr"/>
       <c r="K45" s="6" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
+    </row>
+    <row r="46" ht="130" customHeight="1">
       <c r="A46" s="6" t="n">
         <v>45</v>
       </c>
@@ -3020,7 +2802,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -3030,35 +2812,31 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>a mão e os dedos</t>
+          <t>anel_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>anel_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a mão e os dedos usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr"/>
       <c r="K46" s="6" t="inlineStr"/>
-      <c r="L46" s="6" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
+    </row>
+    <row r="47" ht="130" customHeight="1">
       <c r="A47" s="6" t="n">
         <v>46</v>
       </c>
@@ -3080,35 +2858,31 @@
       <c r="E47" s="6" t="inlineStr"/>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Duas alianças apoiadas lado a lado, uma levemente sobreposta à outra</t>
+          <t>alianca_still-branco-packshot</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>alianca_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Duas alianças apoiadas lado a lado, uma levemente sobreposta à outra.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr"/>
       <c r="K47" s="6" t="inlineStr"/>
-      <c r="L47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
+    </row>
+    <row r="48" ht="130" customHeight="1">
       <c r="A48" s="6" t="n">
         <v>47</v>
       </c>
@@ -3124,7 +2898,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -3134,35 +2908,31 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>as mãos entrelaçadas, próximas ao dedo anelar</t>
+          <t>alianca_still-humanizado</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>alianca_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas as mãos entrelaçadas, próximas ao dedo anelar, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas as mãos entrelaçadas, próximas ao dedo anelar — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Duas alianças apoiadas lado a lado, uma levemente sobreposta à outra, com as mãos entrelaçadas, próximas ao dedo anelar como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com as mãos entrelaçadas, próximas ao dedo anelar levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr"/>
-      <c r="L48" s="6" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
+    </row>
+    <row r="49" ht="130" customHeight="1">
       <c r="A49" s="6" t="n">
         <v>48</v>
       </c>
@@ -3184,35 +2954,31 @@
       <c r="E49" s="6" t="inlineStr"/>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Duas alianças apoiadas lado a lado, uma levemente sobreposta à outra</t>
+          <t>alianca_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>alianca_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Duas alianças apoiadas lado a lado, uma levemente sobreposta à outra.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr"/>
       <c r="K49" s="6" t="inlineStr"/>
-      <c r="L49" s="6" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
+    </row>
+    <row r="50" ht="130" customHeight="1">
       <c r="A50" s="6" t="n">
         <v>49</v>
       </c>
@@ -3234,35 +3000,31 @@
       <c r="E50" s="6" t="inlineStr"/>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Duas alianças apoiadas lado a lado, uma levemente sobreposta à outra</t>
+          <t>alianca_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>alianca_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Duas alianças apoiadas lado a lado, uma levemente sobreposta à outra, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr"/>
-      <c r="L50" s="6" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
+    </row>
+    <row r="51" ht="130" customHeight="1">
       <c r="A51" s="6" t="n">
         <v>50</v>
       </c>
@@ -3278,7 +3040,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -3288,35 +3050,31 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>as mãos entrelaçadas, próximas ao dedo anelar</t>
+          <t>alianca_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>alianca_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas as mãos entrelaçadas, próximas ao dedo anelar, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em as mãos entrelaçadas, próximas ao dedo anelar usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando as mãos entrelaçadas, próximas ao dedo anelar.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr"/>
       <c r="K51" s="6" t="inlineStr"/>
-      <c r="L51" s="6" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
+    </row>
+    <row r="52" ht="130" customHeight="1">
       <c r="A52" s="6" t="n">
         <v>51</v>
       </c>
@@ -3338,35 +3096,31 @@
       <c r="E52" s="6" t="inlineStr"/>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Tornozeleira disposta em curva, simulando o formato do tornozelo</t>
+          <t>tornozeleira_still-branco-packshot</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>tornozeleira_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Tornozeleira disposta em curva, simulando o formato do tornozelo.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr"/>
       <c r="K52" s="6" t="inlineStr"/>
-      <c r="L52" s="6" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
+    </row>
+    <row r="53" ht="130" customHeight="1">
       <c r="A53" s="6" t="n">
         <v>52</v>
       </c>
@@ -3382,7 +3136,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -3392,35 +3146,31 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>o tornozelo e o pé</t>
+          <t>tornozeleira_still-humanizado</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>tornozeleira_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o tornozelo e o pé, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o tornozelo e o pé — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Tornozeleira disposta em curva, simulando o formato do tornozelo, com o tornozelo e o pé como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o tornozelo e o pé levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr"/>
       <c r="K53" s="6" t="inlineStr"/>
-      <c r="L53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
+    </row>
+    <row r="54" ht="130" customHeight="1">
       <c r="A54" s="6" t="n">
         <v>53</v>
       </c>
@@ -3442,35 +3192,31 @@
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Tornozeleira disposta em curva, simulando o formato do tornozelo</t>
+          <t>tornozeleira_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>tornozeleira_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Tornozeleira disposta em curva, simulando o formato do tornozelo.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr"/>
       <c r="K54" s="6" t="inlineStr"/>
-      <c r="L54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
+    </row>
+    <row r="55" ht="130" customHeight="1">
       <c r="A55" s="6" t="n">
         <v>54</v>
       </c>
@@ -3492,35 +3238,31 @@
       <c r="E55" s="6" t="inlineStr"/>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Tornozeleira disposta em curva, simulando o formato do tornozelo</t>
+          <t>tornozeleira_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>tornozeleira_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Tornozeleira disposta em curva, simulando o formato do tornozelo, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr"/>
       <c r="K55" s="6" t="inlineStr"/>
-      <c r="L55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
+    </row>
+    <row r="56" ht="130" customHeight="1">
       <c r="A56" s="6" t="n">
         <v>55</v>
       </c>
@@ -3536,7 +3278,7 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -3546,35 +3288,31 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>o tornozelo e o pé</t>
+          <t>tornozeleira_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>tornozeleira_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o tornozelo e o pé, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o tornozelo e o pé usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o tornozelo e o pé.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr"/>
       <c r="K56" s="6" t="inlineStr"/>
-      <c r="L56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
+    </row>
+    <row r="57" ht="130" customHeight="1">
       <c r="A57" s="6" t="n">
         <v>56</v>
       </c>
@@ -3596,35 +3334,31 @@
       <c r="E57" s="6" t="inlineStr"/>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Broche fixado sobre uma prega de tecido, mostrando o pino e o relevo frontal</t>
+          <t>broche_still-branco-packshot</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>broche_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Broche fixado sobre uma prega de tecido, mostrando o pino e o relevo frontal.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr"/>
       <c r="K57" s="6" t="inlineStr"/>
-      <c r="L57" s="6" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
+    </row>
+    <row r="58" ht="130" customHeight="1">
       <c r="A58" s="6" t="n">
         <v>57</v>
       </c>
@@ -3640,7 +3374,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -3650,35 +3384,31 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>a lapela de um blazer ou tecido</t>
+          <t>broche_still-humanizado</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>broche_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a lapela de um blazer ou prega de tecido, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a lapela de um blazer ou prega de tecido — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Broche fixado sobre uma prega de tecido, mostrando o pino e o relevo frontal, com a lapela de um blazer ou tecido como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com a lapela de um blazer ou tecido levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr"/>
       <c r="K58" s="6" t="inlineStr"/>
-      <c r="L58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
+    </row>
+    <row r="59" ht="130" customHeight="1">
       <c r="A59" s="6" t="n">
         <v>58</v>
       </c>
@@ -3700,35 +3430,31 @@
       <c r="E59" s="6" t="inlineStr"/>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Broche fixado sobre uma prega de tecido, mostrando o pino e o relevo frontal</t>
+          <t>broche_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>broche_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Broche fixado sobre uma prega de tecido, mostrando o pino e o relevo frontal.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr"/>
       <c r="K59" s="6" t="inlineStr"/>
-      <c r="L59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
+    </row>
+    <row r="60" ht="130" customHeight="1">
       <c r="A60" s="6" t="n">
         <v>59</v>
       </c>
@@ -3750,35 +3476,31 @@
       <c r="E60" s="6" t="inlineStr"/>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Broche fixado sobre uma prega de tecido, mostrando o pino e o relevo frontal</t>
+          <t>broche_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>broche_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Broche fixado sobre uma prega de tecido, mostrando o pino e o relevo frontal, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr"/>
       <c r="K60" s="6" t="inlineStr"/>
-      <c r="L60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61" ht="90" customHeight="1">
+    </row>
+    <row r="61" ht="130" customHeight="1">
       <c r="A61" s="6" t="n">
         <v>60</v>
       </c>
@@ -3794,7 +3516,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -3804,35 +3526,31 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>a lapela de um blazer ou tecido</t>
+          <t>broche_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>broche_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a lapela de um blazer ou prega de tecido, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a lapela de um blazer ou prega de tecido usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a lapela de um blazer ou tecido.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr"/>
       <c r="K61" s="6" t="inlineStr"/>
-      <c r="L61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62" ht="90" customHeight="1">
+    </row>
+    <row r="62" ht="130" customHeight="1">
       <c r="A62" s="6" t="n">
         <v>61</v>
       </c>
@@ -3854,35 +3572,31 @@
       <c r="E62" s="6" t="inlineStr"/>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Colar e brincos do conjunto dispostos juntos de forma harmônica</t>
+          <t>conjunto-colar-+-brinco_still-branco-packshot</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>conjunto-colar-+-brinco_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar e brincos do conjunto dispostos juntos de forma harmônica.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr"/>
       <c r="K62" s="6" t="inlineStr"/>
-      <c r="L62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63" ht="90" customHeight="1">
+    </row>
+    <row r="63" ht="130" customHeight="1">
       <c r="A63" s="6" t="n">
         <v>62</v>
       </c>
@@ -3898,7 +3612,7 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -3908,35 +3622,31 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>o pescoço, colo e a orelha</t>
+          <t>conjunto-colar-+-brinco_still-humanizado</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>conjunto-colar-+-brinco_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pescoço, o colo e a orelha, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pescoço, o colo e a orelha — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar e brincos do conjunto dispostos juntos de forma harmônica, com o pescoço, colo e a orelha como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o pescoço, colo e a orelha levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr"/>
       <c r="K63" s="6" t="inlineStr"/>
-      <c r="L63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64" ht="90" customHeight="1">
+    </row>
+    <row r="64" ht="130" customHeight="1">
       <c r="A64" s="6" t="n">
         <v>63</v>
       </c>
@@ -3958,35 +3668,31 @@
       <c r="E64" s="6" t="inlineStr"/>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Colar e brincos do conjunto dispostos juntos de forma harmônica</t>
+          <t>conjunto-colar-+-brinco_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>conjunto-colar-+-brinco_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar e brincos do conjunto dispostos juntos de forma harmônica.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr"/>
       <c r="K64" s="6" t="inlineStr"/>
-      <c r="L64" s="6" t="inlineStr"/>
-    </row>
-    <row r="65" ht="90" customHeight="1">
+    </row>
+    <row r="65" ht="130" customHeight="1">
       <c r="A65" s="6" t="n">
         <v>64</v>
       </c>
@@ -4008,35 +3714,31 @@
       <c r="E65" s="6" t="inlineStr"/>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Colar e brincos do conjunto dispostos juntos de forma harmônica</t>
+          <t>conjunto-colar-+-brinco_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>conjunto-colar-+-brinco_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar e brincos do conjunto dispostos juntos de forma harmônica, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr"/>
       <c r="K65" s="6" t="inlineStr"/>
-      <c r="L65" s="6" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
+    </row>
+    <row r="66" ht="130" customHeight="1">
       <c r="A66" s="6" t="n">
         <v>65</v>
       </c>
@@ -4052,7 +3754,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -4062,35 +3764,31 @@
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>o pescoço, colo e a orelha</t>
+          <t>conjunto-colar-+-brinco_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>conjunto-colar-+-brinco_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pescoço, o colo e a orelha, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pescoço, o colo e a orelha usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pescoço, colo e a orelha.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr"/>
       <c r="K66" s="6" t="inlineStr"/>
-      <c r="L66" s="6" t="inlineStr"/>
-    </row>
-    <row r="67" ht="90" customHeight="1">
+    </row>
+    <row r="67" ht="130" customHeight="1">
       <c r="A67" s="6" t="n">
         <v>66</v>
       </c>
@@ -4112,35 +3810,31 @@
       <c r="E67" s="6" t="inlineStr"/>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Relógio apoiado em pé, mostrando o mostrador de frente e a pulseira em curva</t>
+          <t>relogio_still-branco-packshot</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>relogio_still-branco-packshot</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
+Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Relógio apoiado em pé, mostrando o mostrador de frente e a pulseira em curva.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (#FFFFFF), sem sombras duras, iluminação suave e uniforme tipo softbox, foco nítido em toda a peça, sem reflexos exagerados. Estilo clean, comercial, pronto para catálogo de loja online.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo)</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr"/>
       <c r="K67" s="6" t="inlineStr"/>
-      <c r="L67" s="6" t="inlineStr"/>
-    </row>
-    <row r="68" ht="90" customHeight="1">
+    </row>
+    <row r="68" ht="130" customHeight="1">
       <c r="A68" s="6" t="n">
         <v>67</v>
       </c>
@@ -4156,7 +3850,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Sim (parte do corpo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -4166,35 +3860,31 @@
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>o pulso</t>
+          <t>relogio_still-humanizado</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>relogio_still-humanizado</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Relógio apoiado em pé, mostrando o mostrador de frente e a pulseira em curva, com o pulso como elemento de contexto ao fundo.
-Fotografia still humanizada, profissional, estilo editorial de e-commerce de joias. Foco nítido na peça, com o pulso levemente desfocado(a) ao fundo (profundidade de campo rasa), iluminação natural suave, tom de pele realista: [PERFIL].</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — e-commerce/Instagram)</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr"/>
       <c r="K68" s="6" t="inlineStr"/>
-      <c r="L68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69" ht="90" customHeight="1">
+    </row>
+    <row r="69" ht="130" customHeight="1">
       <c r="A69" s="6" t="n">
         <v>68</v>
       </c>
@@ -4216,35 +3906,31 @@
       <c r="E69" s="6" t="inlineStr"/>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Relógio apoiado em pé, mostrando o mostrador de frente e a pulseira em curva</t>
+          <t>relogio_still-com-sombra-editorial</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>relogio_still-com-sombra-editorial</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Relógio apoiado em pé, mostrando o mostrador de frente e a pulseira em curva.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr"/>
       <c r="K69" s="6" t="inlineStr"/>
-      <c r="L69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70" ht="90" customHeight="1">
+    </row>
+    <row r="70" ht="130" customHeight="1">
       <c r="A70" s="6" t="n">
         <v>69</v>
       </c>
@@ -4266,35 +3952,31 @@
       <c r="E70" s="6" t="inlineStr"/>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Relógio apoiado em pé, mostrando o mostrador de frente e a pulseira em curva</t>
+          <t>relogio_still-em-superficie-texturizada</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>relogio_still-em-superficie-texturizada</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
+Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Relógio apoiado em pé, mostrando o mostrador de frente e a pulseira em curva, apoiado sobre pedra cinza natural.
-Fotografia still profissional sobre superfície pedra cinza natural, com iluminação natural suave vinda de uma janela lateral, sombra natural sutil, composição minimalista e orgânica, cores quentes e aconchegantes.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — feed/catálogo)</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr"/>
       <c r="K70" s="6" t="inlineStr"/>
-      <c r="L70" s="6" t="inlineStr"/>
-    </row>
-    <row r="71" ht="90" customHeight="1">
+    </row>
+    <row r="71" ht="130" customHeight="1">
       <c r="A71" s="6" t="n">
         <v>70</v>
       </c>
@@ -4310,7 +3992,7 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -4320,36 +4002,32 @@
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>o pulso</t>
+          <t>relogio_lifestyle-com-modelo</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>relogio_lifestyle-com-modelo</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
+Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr"/>
       <c r="K71" s="6" t="inlineStr"/>
-      <c r="L71" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L71"/>
+  <autoFilter ref="A1:K71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4367,11 +4045,11 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
@@ -4439,7 +4117,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1">
+    <row r="2" ht="140" customHeight="1">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
@@ -4471,15 +4149,16 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas), um bilhete escrito à mão desfocado ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -4490,7 +4169,7 @@
       <c r="K2" s="6" t="inlineStr"/>
       <c r="L2" s="6" t="inlineStr"/>
     </row>
-    <row r="3" ht="100" customHeight="1">
+    <row r="3" ht="140" customHeight="1">
       <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
@@ -4511,7 +4190,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -4526,15 +4205,16 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas), um bilhete escrito à mão desfocado ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
@@ -4545,7 +4225,7 @@
       <c r="K3" s="6" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr"/>
     </row>
-    <row r="4" ht="100" customHeight="1">
+    <row r="4" ht="140" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
@@ -4577,15 +4257,16 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas), um bilhete escrito à mão desfocado ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -4596,7 +4277,7 @@
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
     </row>
-    <row r="5" ht="100" customHeight="1">
+    <row r="5" ht="140" customHeight="1">
       <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
@@ -4617,7 +4298,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -4632,15 +4313,16 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas), um bilhete escrito à mão desfocado ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -4651,7 +4333,7 @@
       <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr"/>
     </row>
-    <row r="6" ht="100" customHeight="1">
+    <row r="6" ht="140" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
@@ -4683,15 +4365,16 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas), um bilhete escrito à mão desfocado ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -4702,7 +4385,7 @@
       <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="140" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
@@ -4723,7 +4406,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -4738,15 +4421,16 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas), um bilhete escrito à mão desfocado ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -4757,7 +4441,7 @@
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr"/>
     </row>
-    <row r="8" ht="100" customHeight="1">
+    <row r="8" ht="140" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
@@ -4789,15 +4473,16 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas), um bilhete escrito à mão desfocado ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -4808,7 +4493,7 @@
       <c r="K8" s="6" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr"/>
     </row>
-    <row r="9" ht="100" customHeight="1">
+    <row r="9" ht="140" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
@@ -4829,7 +4514,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -4844,15 +4529,16 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas), um bilhete escrito à mão desfocado ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -4863,7 +4549,7 @@
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
     </row>
-    <row r="10" ht="100" customHeight="1">
+    <row r="10" ht="140" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
@@ -4895,15 +4581,16 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -4914,7 +4601,7 @@
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
     </row>
-    <row r="11" ht="100" customHeight="1">
+    <row r="11" ht="140" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
@@ -4935,7 +4622,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -4950,15 +4637,16 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -4969,7 +4657,7 @@
       <c r="K11" s="6" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr"/>
     </row>
-    <row r="12" ht="100" customHeight="1">
+    <row r="12" ht="140" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
@@ -5001,15 +4689,16 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -5020,7 +4709,7 @@
       <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
     </row>
-    <row r="13" ht="100" customHeight="1">
+    <row r="13" ht="140" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
@@ -5041,7 +4730,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -5056,15 +4745,16 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -5075,7 +4765,7 @@
       <c r="K13" s="6" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr"/>
     </row>
-    <row r="14" ht="100" customHeight="1">
+    <row r="14" ht="140" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
@@ -5107,15 +4797,16 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -5126,7 +4817,7 @@
       <c r="K14" s="6" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr"/>
     </row>
-    <row r="15" ht="100" customHeight="1">
+    <row r="15" ht="140" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
@@ -5147,7 +4838,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -5162,15 +4853,16 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -5181,7 +4873,7 @@
       <c r="K15" s="6" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr"/>
     </row>
-    <row r="16" ht="100" customHeight="1">
+    <row r="16" ht="140" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
@@ -5213,15 +4905,16 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -5232,7 +4925,7 @@
       <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr"/>
     </row>
-    <row r="17" ht="100" customHeight="1">
+    <row r="17" ht="140" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
@@ -5253,7 +4946,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -5268,15 +4961,16 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -5287,7 +4981,7 @@
       <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
     </row>
-    <row r="18" ht="100" customHeight="1">
+    <row r="18" ht="140" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>17</v>
       </c>
@@ -5319,15 +5013,16 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
@@ -5338,7 +5033,7 @@
       <c r="K18" s="6" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr"/>
     </row>
-    <row r="19" ht="100" customHeight="1">
+    <row r="19" ht="140" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
@@ -5359,7 +5054,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -5374,15 +5069,16 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -5393,7 +5089,7 @@
       <c r="K19" s="6" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr"/>
     </row>
-    <row r="20" ht="100" customHeight="1">
+    <row r="20" ht="140" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>19</v>
       </c>
@@ -5425,15 +5121,16 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
@@ -5444,7 +5141,7 @@
       <c r="K20" s="6" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr"/>
     </row>
-    <row r="21" ht="100" customHeight="1">
+    <row r="21" ht="140" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
@@ -5465,7 +5162,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -5480,15 +5177,16 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
@@ -5499,7 +5197,7 @@
       <c r="K21" s="6" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr"/>
     </row>
-    <row r="22" ht="100" customHeight="1">
+    <row r="22" ht="140" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>21</v>
       </c>
@@ -5531,15 +5229,16 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -5550,7 +5249,7 @@
       <c r="K22" s="6" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr"/>
     </row>
-    <row r="23" ht="100" customHeight="1">
+    <row r="23" ht="140" customHeight="1">
       <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
@@ -5571,7 +5270,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -5586,15 +5285,16 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -5605,7 +5305,7 @@
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="100" customHeight="1">
+    <row r="24" ht="140" customHeight="1">
       <c r="A24" s="6" t="n">
         <v>23</v>
       </c>
@@ -5637,15 +5337,16 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
@@ -5656,7 +5357,7 @@
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
     </row>
-    <row r="25" ht="100" customHeight="1">
+    <row r="25" ht="140" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
@@ -5677,7 +5378,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -5692,15 +5393,16 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
@@ -5711,7 +5413,7 @@
       <c r="K25" s="6" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="100" customHeight="1">
+    <row r="26" ht="140" customHeight="1">
       <c r="A26" s="6" t="n">
         <v>25</v>
       </c>
@@ -5743,15 +5445,16 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
@@ -5762,7 +5465,7 @@
       <c r="K26" s="6" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr"/>
     </row>
-    <row r="27" ht="100" customHeight="1">
+    <row r="27" ht="140" customHeight="1">
       <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
@@ -5783,7 +5486,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -5798,15 +5501,16 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -5817,7 +5521,7 @@
       <c r="K27" s="6" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr"/>
     </row>
-    <row r="28" ht="100" customHeight="1">
+    <row r="28" ht="140" customHeight="1">
       <c r="A28" s="6" t="n">
         <v>27</v>
       </c>
@@ -5849,15 +5553,16 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
@@ -5868,7 +5573,7 @@
       <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr"/>
     </row>
-    <row r="29" ht="100" customHeight="1">
+    <row r="29" ht="140" customHeight="1">
       <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
@@ -5889,7 +5594,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -5904,15 +5609,16 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -5923,7 +5629,7 @@
       <c r="K29" s="6" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr"/>
     </row>
-    <row r="30" ht="100" customHeight="1">
+    <row r="30" ht="140" customHeight="1">
       <c r="A30" s="6" t="n">
         <v>29</v>
       </c>
@@ -5955,15 +5661,16 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
@@ -5974,7 +5681,7 @@
       <c r="K30" s="6" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr"/>
     </row>
-    <row r="31" ht="100" customHeight="1">
+    <row r="31" ht="140" customHeight="1">
       <c r="A31" s="6" t="n">
         <v>30</v>
       </c>
@@ -5995,7 +5702,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -6010,15 +5717,16 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
@@ -6029,7 +5737,7 @@
       <c r="K31" s="6" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr"/>
     </row>
-    <row r="32" ht="100" customHeight="1">
+    <row r="32" ht="140" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>31</v>
       </c>
@@ -6061,15 +5769,16 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
@@ -6080,7 +5789,7 @@
       <c r="K32" s="6" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr"/>
     </row>
-    <row r="33" ht="100" customHeight="1">
+    <row r="33" ht="140" customHeight="1">
       <c r="A33" s="6" t="n">
         <v>32</v>
       </c>
@@ -6101,7 +5810,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -6116,15 +5825,16 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
@@ -6135,7 +5845,7 @@
       <c r="K33" s="6" t="inlineStr"/>
       <c r="L33" s="6" t="inlineStr"/>
     </row>
-    <row r="34" ht="100" customHeight="1">
+    <row r="34" ht="140" customHeight="1">
       <c r="A34" s="6" t="n">
         <v>33</v>
       </c>
@@ -6167,15 +5877,16 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
@@ -6186,7 +5897,7 @@
       <c r="K34" s="6" t="inlineStr"/>
       <c r="L34" s="6" t="inlineStr"/>
     </row>
-    <row r="35" ht="100" customHeight="1">
+    <row r="35" ht="140" customHeight="1">
       <c r="A35" s="6" t="n">
         <v>34</v>
       </c>
@@ -6207,7 +5918,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -6222,15 +5933,16 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -6241,7 +5953,7 @@
       <c r="K35" s="6" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr"/>
     </row>
-    <row r="36" ht="100" customHeight="1">
+    <row r="36" ht="140" customHeight="1">
       <c r="A36" s="6" t="n">
         <v>35</v>
       </c>
@@ -6273,15 +5985,16 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
@@ -6292,7 +6005,7 @@
       <c r="K36" s="6" t="inlineStr"/>
       <c r="L36" s="6" t="inlineStr"/>
     </row>
-    <row r="37" ht="100" customHeight="1">
+    <row r="37" ht="140" customHeight="1">
       <c r="A37" s="6" t="n">
         <v>36</v>
       </c>
@@ -6313,7 +6026,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -6328,15 +6041,16 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -6347,7 +6061,7 @@
       <c r="K37" s="6" t="inlineStr"/>
       <c r="L37" s="6" t="inlineStr"/>
     </row>
-    <row r="38" ht="100" customHeight="1">
+    <row r="38" ht="140" customHeight="1">
       <c r="A38" s="6" t="n">
         <v>37</v>
       </c>
@@ -6379,15 +6093,16 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
@@ -6398,7 +6113,7 @@
       <c r="K38" s="6" t="inlineStr"/>
       <c r="L38" s="6" t="inlineStr"/>
     </row>
-    <row r="39" ht="100" customHeight="1">
+    <row r="39" ht="140" customHeight="1">
       <c r="A39" s="6" t="n">
         <v>38</v>
       </c>
@@ -6419,7 +6134,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -6434,15 +6149,16 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
@@ -6453,7 +6169,7 @@
       <c r="K39" s="6" t="inlineStr"/>
       <c r="L39" s="6" t="inlineStr"/>
     </row>
-    <row r="40" ht="100" customHeight="1">
+    <row r="40" ht="140" customHeight="1">
       <c r="A40" s="6" t="n">
         <v>39</v>
       </c>
@@ -6485,15 +6201,16 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
@@ -6504,7 +6221,7 @@
       <c r="K40" s="6" t="inlineStr"/>
       <c r="L40" s="6" t="inlineStr"/>
     </row>
-    <row r="41" ht="100" customHeight="1">
+    <row r="41" ht="140" customHeight="1">
       <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
@@ -6525,7 +6242,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -6540,15 +6257,16 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
@@ -6559,7 +6277,7 @@
       <c r="K41" s="6" t="inlineStr"/>
       <c r="L41" s="6" t="inlineStr"/>
     </row>
-    <row r="42" ht="100" customHeight="1">
+    <row r="42" ht="140" customHeight="1">
       <c r="A42" s="6" t="n">
         <v>41</v>
       </c>
@@ -6591,15 +6309,16 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
@@ -6610,7 +6329,7 @@
       <c r="K42" s="6" t="inlineStr"/>
       <c r="L42" s="6" t="inlineStr"/>
     </row>
-    <row r="43" ht="100" customHeight="1">
+    <row r="43" ht="140" customHeight="1">
       <c r="A43" s="6" t="n">
         <v>42</v>
       </c>
@@ -6631,7 +6350,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -6646,15 +6365,16 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
@@ -6665,7 +6385,7 @@
       <c r="K43" s="6" t="inlineStr"/>
       <c r="L43" s="6" t="inlineStr"/>
     </row>
-    <row r="44" ht="100" customHeight="1">
+    <row r="44" ht="140" customHeight="1">
       <c r="A44" s="6" t="n">
         <v>43</v>
       </c>
@@ -6697,15 +6417,16 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
@@ -6716,7 +6437,7 @@
       <c r="K44" s="6" t="inlineStr"/>
       <c r="L44" s="6" t="inlineStr"/>
     </row>
-    <row r="45" ht="100" customHeight="1">
+    <row r="45" ht="140" customHeight="1">
       <c r="A45" s="6" t="n">
         <v>44</v>
       </c>
@@ -6737,7 +6458,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -6752,15 +6473,16 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
@@ -6771,7 +6493,7 @@
       <c r="K45" s="6" t="inlineStr"/>
       <c r="L45" s="6" t="inlineStr"/>
     </row>
-    <row r="46" ht="100" customHeight="1">
+    <row r="46" ht="140" customHeight="1">
       <c r="A46" s="6" t="n">
         <v>45</v>
       </c>
@@ -6803,15 +6525,16 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
@@ -6822,7 +6545,7 @@
       <c r="K46" s="6" t="inlineStr"/>
       <c r="L46" s="6" t="inlineStr"/>
     </row>
-    <row r="47" ht="100" customHeight="1">
+    <row r="47" ht="140" customHeight="1">
       <c r="A47" s="6" t="n">
         <v>46</v>
       </c>
@@ -6843,7 +6566,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -6858,15 +6581,16 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
@@ -6877,7 +6601,7 @@
       <c r="K47" s="6" t="inlineStr"/>
       <c r="L47" s="6" t="inlineStr"/>
     </row>
-    <row r="48" ht="100" customHeight="1">
+    <row r="48" ht="140" customHeight="1">
       <c r="A48" s="6" t="n">
         <v>47</v>
       </c>
@@ -6909,15 +6633,16 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
@@ -6928,7 +6653,7 @@
       <c r="K48" s="6" t="inlineStr"/>
       <c r="L48" s="6" t="inlineStr"/>
     </row>
-    <row r="49" ht="100" customHeight="1">
+    <row r="49" ht="140" customHeight="1">
       <c r="A49" s="6" t="n">
         <v>48</v>
       </c>
@@ -6949,7 +6674,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -6964,15 +6689,16 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
@@ -6983,7 +6709,7 @@
       <c r="K49" s="6" t="inlineStr"/>
       <c r="L49" s="6" t="inlineStr"/>
     </row>
-    <row r="50" ht="100" customHeight="1">
+    <row r="50" ht="140" customHeight="1">
       <c r="A50" s="6" t="n">
         <v>49</v>
       </c>
@@ -7015,15 +6741,16 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
@@ -7034,7 +6761,7 @@
       <c r="K50" s="6" t="inlineStr"/>
       <c r="L50" s="6" t="inlineStr"/>
     </row>
-    <row r="51" ht="100" customHeight="1">
+    <row r="51" ht="140" customHeight="1">
       <c r="A51" s="6" t="n">
         <v>50</v>
       </c>
@@ -7055,7 +6782,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -7070,15 +6797,16 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
@@ -7089,7 +6817,7 @@
       <c r="K51" s="6" t="inlineStr"/>
       <c r="L51" s="6" t="inlineStr"/>
     </row>
-    <row r="52" ht="100" customHeight="1">
+    <row r="52" ht="140" customHeight="1">
       <c r="A52" s="6" t="n">
         <v>51</v>
       </c>
@@ -7121,15 +6849,16 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
@@ -7140,7 +6869,7 @@
       <c r="K52" s="6" t="inlineStr"/>
       <c r="L52" s="6" t="inlineStr"/>
     </row>
-    <row r="53" ht="100" customHeight="1">
+    <row r="53" ht="140" customHeight="1">
       <c r="A53" s="6" t="n">
         <v>52</v>
       </c>
@@ -7161,7 +6890,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -7176,15 +6905,16 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
@@ -7195,7 +6925,7 @@
       <c r="K53" s="6" t="inlineStr"/>
       <c r="L53" s="6" t="inlineStr"/>
     </row>
-    <row r="54" ht="100" customHeight="1">
+    <row r="54" ht="140" customHeight="1">
       <c r="A54" s="6" t="n">
         <v>53</v>
       </c>
@@ -7227,15 +6957,16 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
@@ -7246,7 +6977,7 @@
       <c r="K54" s="6" t="inlineStr"/>
       <c r="L54" s="6" t="inlineStr"/>
     </row>
-    <row r="55" ht="100" customHeight="1">
+    <row r="55" ht="140" customHeight="1">
       <c r="A55" s="6" t="n">
         <v>54</v>
       </c>
@@ -7267,7 +6998,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -7282,15 +7013,16 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
@@ -7301,7 +7033,7 @@
       <c r="K55" s="6" t="inlineStr"/>
       <c r="L55" s="6" t="inlineStr"/>
     </row>
-    <row r="56" ht="100" customHeight="1">
+    <row r="56" ht="140" customHeight="1">
       <c r="A56" s="6" t="n">
         <v>55</v>
       </c>
@@ -7333,15 +7065,16 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
@@ -7352,7 +7085,7 @@
       <c r="K56" s="6" t="inlineStr"/>
       <c r="L56" s="6" t="inlineStr"/>
     </row>
-    <row r="57" ht="100" customHeight="1">
+    <row r="57" ht="140" customHeight="1">
       <c r="A57" s="6" t="n">
         <v>56</v>
       </c>
@@ -7373,7 +7106,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -7388,15 +7121,16 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
@@ -7407,7 +7141,7 @@
       <c r="K57" s="6" t="inlineStr"/>
       <c r="L57" s="6" t="inlineStr"/>
     </row>
-    <row r="58" ht="100" customHeight="1">
+    <row r="58" ht="140" customHeight="1">
       <c r="A58" s="6" t="n">
         <v>57</v>
       </c>
@@ -7439,15 +7173,16 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Um par de brincos posicionado lado a lado, simetricamente.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
@@ -7458,7 +7193,7 @@
       <c r="K58" s="6" t="inlineStr"/>
       <c r="L58" s="6" t="inlineStr"/>
     </row>
-    <row r="59" ht="100" customHeight="1">
+    <row r="59" ht="140" customHeight="1">
       <c r="A59" s="6" t="n">
         <v>58</v>
       </c>
@@ -7479,7 +7214,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -7494,15 +7229,16 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a orelha e lateral do rosto.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
@@ -7513,7 +7249,7 @@
       <c r="K59" s="6" t="inlineStr"/>
       <c r="L59" s="6" t="inlineStr"/>
     </row>
-    <row r="60" ht="100" customHeight="1">
+    <row r="60" ht="140" customHeight="1">
       <c r="A60" s="6" t="n">
         <v>59</v>
       </c>
@@ -7545,15 +7281,16 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Colar disposto de forma orgânica sobre a superfície, mostrando o fecho e o comprimento total.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
@@ -7564,7 +7301,7 @@
       <c r="K60" s="6" t="inlineStr"/>
       <c r="L60" s="6" t="inlineStr"/>
     </row>
-    <row r="61" ht="100" customHeight="1">
+    <row r="61" ht="140" customHeight="1">
       <c r="A61" s="6" t="n">
         <v>60</v>
       </c>
@@ -7585,7 +7322,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -7600,15 +7337,16 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o colo e o pescoço.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
@@ -7619,7 +7357,7 @@
       <c r="K61" s="6" t="inlineStr"/>
       <c r="L61" s="6" t="inlineStr"/>
     </row>
-    <row r="62" ht="100" customHeight="1">
+    <row r="62" ht="140" customHeight="1">
       <c r="A62" s="6" t="n">
         <v>61</v>
       </c>
@@ -7651,15 +7389,16 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Anel apoiado em pé, levemente inclinado, mostrando o aro e o detalhe frontal.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
@@ -7670,7 +7409,7 @@
       <c r="K62" s="6" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
     </row>
-    <row r="63" ht="100" customHeight="1">
+    <row r="63" ht="140" customHeight="1">
       <c r="A63" s="6" t="n">
         <v>62</v>
       </c>
@@ -7691,7 +7430,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -7706,15 +7445,16 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando a mão e os dedos.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
@@ -7725,7 +7465,7 @@
       <c r="K63" s="6" t="inlineStr"/>
       <c r="L63" s="6" t="inlineStr"/>
     </row>
-    <row r="64" ht="100" customHeight="1">
+    <row r="64" ht="140" customHeight="1">
       <c r="A64" s="6" t="n">
         <v>63</v>
       </c>
@@ -7757,15 +7497,16 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: Pulseira disposta em curva, como se estivesse ao redor de um pulso invisível.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
-Fotografia still editorial profissional. Fundo neutro (cinza claro ou bege), com sombra suave e alongada da peça projetada de forma elegante, iluminação direcional lateral suave, alto contraste controlado, clima sofisticado e minimalista.</t>
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>1:1 (quadrado — catálogo/editorial)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
@@ -7776,7 +7517,7 @@
       <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
     </row>
-    <row r="65" ht="100" customHeight="1">
+    <row r="65" ht="140" customHeight="1">
       <c r="A65" s="6" t="n">
         <v>64</v>
       </c>
@@ -7797,7 +7538,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Sim (modelo completo)</t>
+          <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -7812,15 +7553,16 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Usando como base a foto anexada da peça (semijoia real), gere uma nova fotografia profissional dessa MESMA peça. É obrigatório preservar com fidelidade absoluta: formato, cor e acabamento do metal, tipo e corte das pedras/cristais, textura, brilho, tamanho e proporções. NÃO altere, substitua, invente ou modifique a peça de nenhuma forma — a joia gerada precisa ser 100% reconhecível como a peça original.
-Cena: [PERFIL] usando a peça de forma natural, evidenciando o pulso.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
-Fotografia lifestyle profissional para redes sociais e e-commerce, com [PERFIL] usando a peça em cena natural do dia a dia, expressão espontânea e sutil, iluminação natural suave (luz de janela ou luz externa suave), fundo desfocado (profundidade de campo rasa), clima autêntico e aspiracional.</t>
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>4:5 (vertical — Instagram/Stories)</t>
+          <t>3:4 (vertical)</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">

--- a/content/Photo_Studio_TPV_Biblioteca_de_Prompts.xlsx
+++ b/content/Photo_Studio_TPV_Biblioteca_de_Prompts.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -771,7 +771,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -817,7 +817,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -863,7 +863,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -913,7 +913,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -959,7 +959,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pescoço, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pescoço — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pescoço, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pescoço usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo e o decote, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo e o decote — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo e o decote, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo e o decote usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, próximo ao centro do peito, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, próximo ao centro do peito — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, próximo ao centro do peito, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo, próximo ao centro do peito usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o peito e a base do pescoço, com estilo masculino, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o peito e a base do pescoço, com estilo masculino — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o peito e a base do pescoço, com estilo masculino, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o peito e a base do pescoço, com estilo masculino usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso e o antebraço, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso e o antebraço — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso e o antebraço, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso e o antebraço usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a mão e os dedos usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas as mãos entrelaçadas, próximas ao dedo anelar, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas as mãos entrelaçadas, próximas ao dedo anelar — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas as mãos entrelaçadas, próximas ao dedo anelar, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em as mãos entrelaçadas, próximas ao dedo anelar usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o tornozelo e o pé, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o tornozelo e o pé — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o tornozelo e o pé, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o tornozelo e o pé usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a lapela de um blazer ou prega de tecido, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a lapela de um blazer ou prega de tecido — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a lapela de um blazer ou prega de tecido, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a lapela de um blazer ou prega de tecido usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pescoço, o colo e a orelha, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pescoço, o colo e a orelha — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pescoço, o colo e a orelha, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pescoço, o colo e a orelha usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -4205,7 +4205,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -4257,7 +4257,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -4313,7 +4313,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -4365,7 +4365,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -4421,7 +4421,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -4473,7 +4473,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -4529,7 +4529,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -4581,7 +4581,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -4637,7 +4637,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -4689,7 +4689,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -4745,7 +4745,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -4797,7 +4797,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -4853,7 +4853,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -4905,7 +4905,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -4961,7 +4961,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5069,7 +5069,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5121,7 +5121,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5229,7 +5229,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5285,7 +5285,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5337,7 +5337,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5393,7 +5393,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5445,7 +5445,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5501,7 +5501,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5609,7 +5609,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5661,7 +5661,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5717,7 +5717,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5825,7 +5825,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5877,7 +5877,7 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -5933,7 +5933,7 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -5985,7 +5985,7 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6041,7 +6041,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6093,7 +6093,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6149,7 +6149,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6257,7 +6257,7 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6309,7 +6309,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6365,7 +6365,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6417,7 +6417,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6525,7 +6525,7 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6581,7 +6581,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6633,7 +6633,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6689,7 +6689,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6741,7 +6741,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6797,7 +6797,7 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6849,7 +6849,7 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -6905,7 +6905,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -6957,7 +6957,7 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -7065,7 +7065,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -7121,7 +7121,7 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -7229,7 +7229,7 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -7281,7 +7281,7 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -7337,7 +7337,7 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -7389,7 +7389,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -7445,7 +7445,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
@@ -7497,7 +7497,7 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
@@ -7553,7 +7553,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.

--- a/content/Photo_Studio_TPV_Biblioteca_de_Prompts.xlsx
+++ b/content/Photo_Studio_TPV_Biblioteca_de_Prompts.xlsx
@@ -721,10 +721,10 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
@@ -771,10 +771,10 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -817,10 +817,10 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -863,10 +863,10 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -913,10 +913,10 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -959,10 +959,10 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1009,10 +1009,10 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1055,10 +1055,10 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -1101,10 +1101,10 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1151,10 +1151,10 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1197,10 +1197,10 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1247,10 +1247,10 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pescoço, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pescoço — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1293,10 +1293,10 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1339,10 +1339,10 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça em uma curva aberta e levemente assimétrica sobre a superfície, sugerindo o formato do pescoço sem formar um círculo perfeito ou fechado.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1389,10 +1389,10 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pescoço, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pescoço usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1435,10 +1435,10 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -1485,10 +1485,10 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo e o decote, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo e o decote — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1531,10 +1531,10 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1577,10 +1577,10 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente formando curvas amplas, orgânicas e assimétricas — nunca curvas espelhadas ou geométricas. Deixe o pingente (ou uma das extremidades) como ponto focal da composição, com o restante se estendendo de forma natural, como se tivesse acabado de cair sobre a superfície.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1627,10 +1627,10 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo e o decote, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo e o decote usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -1673,10 +1673,10 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1723,10 +1723,10 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, próximo ao centro do peito, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, próximo ao centro do peito — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -1769,10 +1769,10 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1815,10 +1815,10 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o pingente como protagonista absoluto, com a corrente caindo ao redor em curvas orgânicas e assimétricas — nunca círculos, ovais ou formas espelhadas dos dois lados.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -1865,10 +1865,10 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, próximo ao centro do peito, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o colo, próximo ao centro do peito usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1911,10 +1911,10 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -1961,10 +1961,10 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o peito e a base do pescoço, com estilo masculino, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o peito e a base do pescoço, com estilo masculino — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -2007,10 +2007,10 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -2053,10 +2053,10 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a corrente em uma curva reta a levemente ondulada, transmitindo peso e robustez — nunca curvas perfeitamente simétricas ou decorativas demais.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -2103,10 +2103,10 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o peito e a base do pescoço, com estilo masculino, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o peito e a base do pescoço, com estilo masculino usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -2149,10 +2149,10 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -2199,10 +2199,10 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -2245,10 +2245,10 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2291,10 +2291,10 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -2341,10 +2341,10 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -2387,10 +2387,10 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -2437,10 +2437,10 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso e o antebraço, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso e o antebraço — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
@@ -2483,10 +2483,10 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
@@ -2529,10 +2529,10 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o bracelete em pé, com o eixo central perpendicular à superfície (aproximadamente 90°) e inclinação máxima de 3° — o suficiente apenas para evitar aparência artificial de renderização. O centro de gravidade deve estar exatamente sobre o ponto de apoio, sem parecer tombado ou flutuando. A peça deve ocupar cerca de 65% da altura da imagem.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -2579,10 +2579,10 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso e o antebraço, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso e o antebraço usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -2625,10 +2625,10 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2675,10 +2675,10 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -2721,10 +2721,10 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -2767,10 +2767,10 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -2817,10 +2817,10 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a mão e os dedos usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
@@ -2863,10 +2863,10 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -2913,10 +2913,10 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas as mãos entrelaçadas, próximas ao dedo anelar, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas as mãos entrelaçadas, próximas ao dedo anelar — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente duas mãos entrelaçadas, cada uma com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou deformados. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -2959,10 +2959,10 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
@@ -3005,10 +3005,10 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione as duas alianças em pé, lado a lado, uma levemente sobreposta à outra, ambas fisicamente equilibradas sobre a superfície — nunca flutuando.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
@@ -3055,10 +3055,10 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas as mãos entrelaçadas, próximas ao dedo anelar, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em as mãos entrelaçadas, próximas ao dedo anelar usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente duas mãos entrelaçadas, cada uma com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou deformados. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -3101,10 +3101,10 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
@@ -3151,10 +3151,10 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o tornozelo e o pé, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o tornozelo e o pé — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um tornozelo e um pé, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras ou deformados. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -3197,10 +3197,10 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -3243,10 +3243,10 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a peça formando uma curva aberta e natural, como se tivesse caído sobre a superfície — nunca um círculo perfeitamente fechado.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -3293,10 +3293,10 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o tornozelo e o pé, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o tornozelo e o pé usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um tornozelo e um pé, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras ou deformados. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
@@ -3339,10 +3339,10 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
@@ -3389,10 +3389,10 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a lapela de um blazer ou prega de tecido, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a lapela de um blazer ou prega de tecido — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
@@ -3435,10 +3435,10 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -3481,10 +3481,10 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o broche sobre uma prega de tecido, mostrando claramente o pino e o relevo frontal da peça, sem parecer flutuando.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -3531,10 +3531,10 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a lapela de um blazer ou prega de tecido, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em a lapela de um blazer ou prega de tecido usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -3577,10 +3577,10 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -3627,10 +3627,10 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pescoço, o colo e a orelha, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pescoço, o colo e a orelha — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -3673,10 +3673,10 @@
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -3719,10 +3719,10 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Utilize exatamente as peças presentes na foto anexada, na mesma quantidade — nunca adicione, remova ou duplique nenhuma joia. Se não houver um tipo de peça na foto, não crie esse tipo de peça. Organize cada peça de acordo com seu próprio comportamento físico (colar em curvas orgânicas e assimétricas; brincos próximos entre si, mostrando a face principal), distribuindo os elementos em diferentes regiões da composição para um equilíbrio visual sofisticado, porém não perfeitamente simétrico.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -3769,10 +3769,10 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pescoço, o colo e a orelha, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pescoço, o colo e a orelha usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -3815,10 +3815,10 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
 Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
@@ -3865,10 +3865,10 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
@@ -3911,10 +3911,10 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -3957,10 +3957,10 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
 Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
@@ -4007,10 +4007,10 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -4149,11 +4149,11 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -4205,11 +4205,11 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -4257,11 +4257,11 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -4313,11 +4313,11 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -4365,11 +4365,11 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -4421,11 +4421,11 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -4529,11 +4529,11 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -4581,11 +4581,11 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -4637,11 +4637,11 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -4689,11 +4689,11 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -4797,11 +4797,11 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -4853,11 +4853,11 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -4905,11 +4905,11 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -4961,11 +4961,11 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -5013,11 +5013,11 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -5069,11 +5069,11 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -5121,11 +5121,11 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -5177,11 +5177,11 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -5229,11 +5229,11 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -5285,11 +5285,11 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -5337,11 +5337,11 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -5445,11 +5445,11 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -5501,11 +5501,11 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -5553,11 +5553,11 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -5609,11 +5609,11 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -5661,11 +5661,11 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -5717,11 +5717,11 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -5769,11 +5769,11 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
@@ -5825,11 +5825,11 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -5877,11 +5877,11 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
@@ -5933,11 +5933,11 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -5985,11 +5985,11 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -6041,11 +6041,11 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -6149,11 +6149,11 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -6201,11 +6201,11 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -6257,11 +6257,11 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Dia Internacional da Mulher. Paleta de cores: tons de roxo e violeta. Elementos/props de cena: flor de mimosa (amarela) desfocada ao fundo. Clima geral: moderno, empoderado e sofisticado.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -6309,11 +6309,11 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -6365,11 +6365,11 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -6417,11 +6417,11 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -6473,11 +6473,11 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -6525,11 +6525,11 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -6633,11 +6633,11 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -6689,11 +6689,11 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -6741,11 +6741,11 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
@@ -6797,11 +6797,11 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -6849,11 +6849,11 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
@@ -6905,11 +6905,11 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
@@ -7013,11 +7013,11 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
@@ -7065,11 +7065,11 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -7121,11 +7121,11 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
@@ -7173,11 +7173,11 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
@@ -7229,11 +7229,11 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -7281,11 +7281,11 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
@@ -7337,11 +7337,11 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -7389,11 +7389,11 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -7445,11 +7445,11 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -7497,11 +7497,11 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
@@ -7553,11 +7553,11 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
 Tema visual: Consciência Negra. Paleta de cores: tons terrosos e dourados. Elementos/props de cena: tecido com estampa de padronagem africana desfocado ao fundo. Clima geral: de valorização, orgulho e sofisticação.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme que a peça gerada corresponde exatamente, em quantidade e em detalhes, à peça da imagem original. Formato final da imagem: 3:4 (vertical).</t>
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">

--- a/content/Photo_Studio_TPV_Biblioteca_de_Prompts.xlsx
+++ b/content/Photo_Studio_TPV_Biblioteca_de_Prompts.xlsx
@@ -10,10 +10,12 @@
     <sheet name="Instruções" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Evergreen" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Datas Comemorativas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Expositores" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evergreen'!$A$1:$K$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Datas Comemorativas'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Evergreen'!$A$1:$K$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Datas Comemorativas'!$A$1:$L$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Expositores'!$A$1:$K$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -621,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3788,246 +3790,8 @@
       <c r="J66" s="6" t="inlineStr"/>
       <c r="K66" s="6" t="inlineStr"/>
     </row>
-    <row r="67" ht="130" customHeight="1">
-      <c r="A67" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Relógio</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Still Branco (Packshot)</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>relogio_still-branco-packshot</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
-Fotografia still de produto (packshot) profissional para e-commerce. Fundo branco puro (RGB 255,255,255), infinito, sem linha de horizonte, sem gradientes, sem textura e sem qualquer elemento decorativo. Iluminação de estúdio: uma fonte de luz principal ampla e difusa, uma luz de preenchimento suave do lado oposto para controlar sombras, e uma luz de contorno sutil para destacar a silhueta. Reflexos no metal limpos, contínuos e fisicamente corretos, sem brilhos estourados. Sombra de contato única, suave e difusa, com leve gradiente natural logo abaixo da peça. Lente equivalente entre 85mm e 105mm, foco perfeitamente nítido em toda a peça, sem distorção de perspectiva.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="6" t="inlineStr"/>
-    </row>
-    <row r="68" ht="130" customHeight="1">
-      <c r="A68" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Relógio</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Still Humanizado</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Sim (parte do corpo, sem rosto)</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Mulher adulta (30-45), pele morena | Homem adulto (35-50), pele clara | Mulher idosa (60+), pele negra</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>relogio_still-humanizado</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
-Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr"/>
-      <c r="K68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69" ht="130" customHeight="1">
-      <c r="A69" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Relógio</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Still com Sombra Editorial</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr"/>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>relogio_still-com-sombra-editorial</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
-Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr"/>
-      <c r="K69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70" ht="130" customHeight="1">
-      <c r="A70" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Relógio</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Still em Superfície Texturizada</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr"/>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>relogio_still-em-superficie-texturizada</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: Posicione o relógio em pé, mostrando o mostrador de frente, com a pulseira formando uma curva aberta e natural ao redor — fisicamente equilibrado, nunca flutuando ou tombado.
-Fotografia still editorial sobre uma superfície de linho bege, de formato orgânico e bordas irregulares, apoiada sobre um tecido acetinado em tom bege claro e quente. Câmera em perspectiva oblíqua, entre 45° e 55° acima da superfície — nunca totalmente frontal nem top-down perfeitamente perpendicular; a composição pode aparecer levemente rotacionada dentro do quadro. Iluminação profissional de estúdio inspirada em luz solar suave entrando lateralmente, criando sombras pequenas e realistas que mostram a peça fisicamente apoiada sobre a superfície. Contraste moderado, cena clara, quente e sofisticada — evitar sombras muito escuras ou iluminação dramática.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="inlineStr"/>
-      <c r="K70" s="6" t="inlineStr"/>
-    </row>
-    <row r="71" ht="130" customHeight="1">
-      <c r="A71" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>Relógio</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle com Modelo</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>Sim (parte do corpo, sem rosto)</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>Mulher adulta (30-45), pele morena | Homem adulto (35-50), pele clara | Mulher idosa (60+), pele negra</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>relogio_lifestyle-com-modelo</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
-Fotografia lifestyle editorial para redes sociais e e-commerce. Enquadramento fechado o suficiente para não mostrar o rosto da modelo — foco em o pulso usando a peça de forma natural, em um gesto espontâneo do dia a dia, compatível com o tipo de peça. Iluminação natural suave, como luz de uma janela lateral ampla, sem fonte artificial. Fundo desfocado (profundidade de campo rasa), sugerindo um ambiente interno elegante e minimalista, sem elementos que disputem atenção com a joia. Tons neutros e quentes (branco, off-white, bege). A peça deve permanecer perfeitamente nítida e iluminada, com reflexos naturais e fisicamente corretos no metal.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr"/>
-      <c r="K71" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K71"/>
+  <autoFilter ref="A1:K66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4038,7 +3802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4123,7 +3887,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Dia das Mães</t>
+          <t>Natal</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -4144,10 +3908,442 @@
       <c r="F2" s="6" t="inlineStr"/>
       <c r="G2" s="6" t="inlineStr">
         <is>
+          <t>natal_brinco_still-com-tema</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
+Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr"/>
+      <c r="L2" s="6" t="inlineStr"/>
+    </row>
+    <row r="3" ht="140" customHeight="1">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Natal</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Brinco</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle com Tema</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Sim (parte do corpo, sem rosto)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>natal_brinco_lifestyle-com-tema</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
+Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="140" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Natal</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Colar</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Still com Tema</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>natal_colar_still-com-tema</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
+Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="140" customHeight="1">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Natal</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Colar</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle com Tema</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Sim (parte do corpo, sem rosto)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>natal_colar_lifestyle-com-tema</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
+Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="140" customHeight="1">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Natal</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Anel</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Still com Tema</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>natal_anel_still-com-tema</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
+Tema visual: Natal. Paleta de cores: tons de vermelho, dourado e verde. Elementos/props de cena: ramos verdes, pinha desfocada, luzes de natal desfocadas ao fundo (efeito bokeh dourado). Clima geral: aconchegante, festivo e brilhante.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="140" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Dia das Mães</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Anel</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle com Tema</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Sim (parte do corpo, sem rosto)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>dia-das-maes_anel_lifestyle-com-tema</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="140" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Dia das Mães</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Pulseira</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Still com Tema</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>dia-das-maes_pulseira_still-com-tema</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Dia das Mães</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Pulseira</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Lifestyle com Tema</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Sim (parte do corpo, sem rosto)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>dia-das-maes_pulseira_lifestyle-com-tema</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
+Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
+Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
+Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
+Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Dia das Mães</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Brinco</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Still com Tema</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
           <t>dia-das-maes_brinco_still-com-tema</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
@@ -4156,54 +4352,54 @@
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr"/>
-      <c r="L2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3" ht="140" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>3:4 (vertical)</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>A gerar</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Dia das Mães</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Brinco</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Lifestyle com Tema</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Sim (parte do corpo, sem rosto)</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>dia-das-maes_brinco_lifestyle-com-tema</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
@@ -4212,438 +4408,6 @@
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr"/>
-      <c r="L3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4" ht="140" customHeight="1">
-      <c r="A4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Dia das Mães</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Colar</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Still com Tema</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>dia-das-maes_colar_still-com-tema</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr"/>
-      <c r="L4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="140" customHeight="1">
-      <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Dia das Mães</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Colar</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle com Tema</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Sim (parte do corpo, sem rosto)</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>dia-das-maes_colar_lifestyle-com-tema</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="140" customHeight="1">
-      <c r="A6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Dia das Mães</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Anel</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Still com Tema</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>dia-das-maes_anel_still-com-tema</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="140" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Dia das Mães</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Anel</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle com Tema</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Sim (parte do corpo, sem rosto)</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>dia-das-maes_anel_lifestyle-com-tema</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="140" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Dia das Mães</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Pulseira</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Still com Tema</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>dia-das-maes_pulseira_still-com-tema</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr"/>
-      <c r="L8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="140" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Dia das Mães</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Pulseira</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle com Tema</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Sim (parte do corpo, sem rosto)</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>dia-das-maes_pulseira_lifestyle-com-tema</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
-Tema visual: Dia das Mães. Paleta de cores: tons de rosa suave e nude. Elementos/props de cena: flores (rosas) desfocadas ao fundo, tecido de seda rosa-claro. Clima geral: afetivo, delicado e caloroso.
-Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr"/>
-      <c r="L9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10" ht="140" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Dia dos Namorados</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Brinco</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Still com Tema</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>dia-dos-namorados_brinco_still-com-tema</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
-Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr"/>
-      <c r="L10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="140" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Dia dos Namorados</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Brinco</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle com Tema</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Sim (parte do corpo, sem rosto)</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>dia-dos-namorados_brinco_lifestyle-com-tema</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
-Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
-Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>3:4 (vertical)</t>
@@ -4931,7 +4695,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Dia dos Namorados</t>
+          <t>Black Friday</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4956,14 +4720,14 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>dia-dos-namorados_pulseira_lifestyle-com-tema</t>
+          <t>black-friday_pulseira_lifestyle-com-tema</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
-Tema visual: Dia dos Namorados. Paleta de cores: tons de vermelho e vinho. Elementos/props de cena: pétalas de rosa vermelha, velas acesas desfocadas ao fundo. Clima geral: romântico, intimista, iluminação quente e noturna.
+Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente um pulso e uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, fundidos ou uma segunda mão aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
@@ -4987,7 +4751,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Dia das Crianças</t>
+          <t>Black Friday</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -5008,14 +4772,14 @@
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>dia-das-criancas_brinco_still-com-tema</t>
+          <t>black-friday_brinco_still-com-tema</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Deixe um brinco apoiado em pé, em ângulo de aproximadamente 45° em relação à câmera, e o outro brinco deitado naturalmente sobre a superfície ao lado. Caso a peça tenha tarraxa, mantenha uma tarraxa presa em cada brinco — nunca deixe a tarraxa solta ou separada da peça.
-Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
+Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
@@ -5039,7 +4803,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Dia das Crianças</t>
+          <t>Black Friday</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -5064,14 +4828,14 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>dia-das-criancas_brinco_lifestyle-com-tema</t>
+          <t>black-friday_brinco_lifestyle-com-tema</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto), evidenciando a peça de forma natural.
-Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
+Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a orelha e a lateral do rosto (apenas esses elementos — não mostrar o restante do rosto) — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Garanta anatomia perfeita da orelha e do lóbulo — sem deformações, sem uma segunda orelha ou rosto fantasma aparecendo no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
@@ -5095,7 +4859,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Dia das Crianças</t>
+          <t>Black Friday</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -5116,14 +4880,14 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>dia-das-criancas_colar_still-com-tema</t>
+          <t>black-friday_colar_still-com-tema</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Apoie o colar completamente sobre a superfície, deixando a corrente cair em curvas amplas e orgânicas, como o peso natural do metal realmente se comportaria — nunca reproduza o formato exato da foto original. Nunca crie círculos perfeitos, ovais, corações, gotas ou curvas espelhadas/simétricas dos dois lados; cada lado da corrente deve ter um desenho diferente, com raios e comprimentos de curva variados. Se houver pingente, ele deve ser o ponto focal da composição.
-Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
+Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
@@ -5147,7 +4911,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Dia das Crianças</t>
+          <t>Black Friday</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -5172,14 +4936,14 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>dia-das-criancas_colar_lifestyle-com-tema</t>
+          <t>black-friday_colar_lifestyle-com-tema</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
           <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: mostrar apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula, evidenciando a peça de forma natural.
-Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
+Tema visual: Black Friday. Paleta de cores: preto e dourado. Elementos/props de cena: fundo preto fosco, iluminação dramática lateral, reflexo dourado sutil. Clima geral: luxuoso, de destaque, alto contraste.
 Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o colo, as clavículas e a parte inferior do pescoço, terminando imediatamente abaixo da mandíbula — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
@@ -5203,7 +4967,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Dia das Crianças</t>
+          <t>Dia dos Pais</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -5224,14 +4988,14 @@
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>dia-das-criancas_anel_still-com-tema</t>
+          <t>dia-dos-pais_anel_still-com-tema</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
 Composição: Posicione o anel em pé, levemente inclinado, mostrando claramente o aro e o detalhe frontal (pedra ou desenho principal). A peça deve parecer fisicamente apoiada e equilibrada, nunca flutuando ou tombada.
-Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
+Tema visual: Dia dos Pais. Paleta de cores: tons de azul-marinho e cinza-grafite. Elementos/props de cena: madeira escura, textura de couro ao fundo desfocado. Clima geral: sóbrio, elegante e masculino.
 Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
 Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
         </is>
@@ -5255,7 +5019,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Dia das Crianças</t>
+          <t>Dia dos Pais</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -5280,442 +5044,10 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>dia-das-criancas_anel_lifestyle-com-tema</t>
+          <t>dia-dos-pais_anel_lifestyle-com-tema</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: mostrar apenas a mão e os dedos, evidenciando a peça de forma natural.
-Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas a mão e os dedos — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das indicadas. A pele deve ter aparência extremamente natural, saudável e uniforme, com tom: [PERFIL]. Criar uma única faixa de sombra diagonal, contínua e bem definida, inclinada aproximadamente 45°, atravessando a composição como luz entrando por uma janela — a sombra nunca deve cruzar ou escurecer a peça, que deve permanecer completamente iluminada e em destaque. Vestuário minimalista em tecido acetinado ou seda fosca, em tom off-white, extremamente discreto para não competir com a joia. Lente equivalente entre 85mm e 105mm, profundidade de campo rasa — a pele pode ficar levemente desfocada, mas a peça deve permanecer perfeitamente nítida. Fundo neutro (cinza quente muito suave ou bege acinzentado), sem textura, objetos ou elementos decorativos. Não adicionar outras joias, acessórios ou maquiagem chamativa.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Mostre exatamente uma mão, com exatamente cinco dedos anatomicamente corretos — nunca dedos extras, dedos fundidos, articulações deformadas ou uma segunda mão/braço aparecendo parcialmente no enquadramento. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="140" customHeight="1">
-      <c r="A24" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Dia das Crianças</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Pulseira</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Still com Tema</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>dia-das-criancas_pulseira_still-com-tema</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: Apoie a pulseira formando uma curva aberta e natural sobre a superfície, como se tivesse caído naturalmente — nunca um círculo perfeitamente fechado.
-Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia editorial de joias com estética minimalista, sofisticada e contemporânea, semelhante a campanhas de marcas de luxo. A peça deve estar apoiada sobre um tecido branco ou off-white premium, fosco, encorpado, com textura delicada semelhante a crepe de seda estruturado, moldado à mão em ondas amplas e curvas orgânicas — nunca padrões repetitivos, simetria perfeita ou dobras geométricas/espirais matematicamente exatas (isso denuncia aparência de imagem gerada por IA). Câmera em ângulo de aproximadamente 45°, lente macro equivalente a 85-100mm, enquadramento em close-up com a peça ocupando cerca da metade da imagem. Iluminação natural extremamente suave e difusa, como luz de uma grande janela lateral, criando sombras delicadas entre as dobras do tecido. Paleta restrita a branco quente, marfim e creme suave. Não adicionar flores, folhas, pedras decorativas, madeira, embalagens, mãos, pessoas ou qualquer elemento decorativo.
-Qualidade: altíssima resolução, nitidez máxima na joia, excelente alcance dinâmico, texturas naturais, reflexos fisicamente corretos, cores absolutamente fiéis, acabamento fotográfico profissional. Eliminar completamente aparência de renderização 3D, ruído digital, granulado, halos ou qualquer aspecto artificial típico de imagem gerada por IA. A peça não deve parecer flutuando, tombada ou fora de escala — preserve rigorosamente suas proporções e comportamento físico real. Antes de finalizar, confirme item por item: a quantidade de peças geradas é idêntica à da foto original (nem a mais, nem a menos); nenhuma peça, pingente ou pedra foi inventado, duplicado ou removido; todos os detalhes de acabamento batem com o original. Formato final da imagem: 3:4 (vertical).</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>3:4 (vertical)</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>A gerar</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr"/>
-      <c r="L24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="140" customHeight="1">
-      <c r="A25" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Dia das Crianças</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Pulseira</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Lifestyle com Tema</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Sim (parte do corpo, sem rosto)</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Mulher jovem (18-25), pele clara | Mulher adulta (30-45), pele morena | Mulher adulta (30-45), pele negra | Mulher idosa (60+), pele clara</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>dia-das-criancas_pulseira_lifestyle-com-tema</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Utilize exclusivamente a joia da fotografia anexada como referência do produto. Antes de gerar, identifique exatamente quantas peças e quantas unidades de cada peça existem na fotografia anexada (por exemplo, um par de brincos conta como duas unidades) e reproduza exatamente essa mesma quantidade na imagem final — nunca invente, duplique, repita, clone, remova ou complete o conjunto adicionando peças, pingentes, pedras ou componentes que não estejam fisicamente presentes na foto original. Se a foto anexada não contiver determinado tipo de peça (por exemplo, não houver anel), essa peça não deve aparecer na imagem final sob nenhuma hipótese. Preserve com fidelidade absoluta: formato, proporções, espessura, acabamento, brilho, textura, cor do metal, pedras (corte, tamanho e posição), cravação, fechos e elos, e todos os demais detalhes originais da peça. Não redesenhe, reinterprete, estilize, complete, corrija ou invente nenhuma característica da joia — reproduza exatamente o que existe na imagem original. Não utilize a foto anexada como referência de cenário, iluminação, enquadramento ou composição — ela serve apenas para identificar a peça, sua quantidade exata e seus detalhes exatos; remova completamente quaisquer objetos, mãos ou fundos presentes na foto original. Atenção especial à espessura de correntes, elos e fios: é um erro comum de IA generativa deixar correntes finas e delicadas mais grossas, mais vistosas ou mais robustas do que a peça real. A corrente gerada precisa ter exatamente a mesma espessura, o mesmo diâmetro de elo e a mesma delicadeza da foto original — NUNCA mais grossa, mais larga ou mais chamativa do que o original, mesmo que isso a deixe visualmente mais sutil ou difícil de perceber na imagem gerada.
-Composição: mostrar apenas o pulso, evidenciando a peça de forma natural.
-Tema visual: Dia das Crianças. Paleta de cores: tons pastéis vibrantes (amarelo, azul-bebê, rosa-claro). Elementos/props de cena: pequenos balões desfocados ao fundo, ambiente lúdico. Clima geral: leve, alegre e descontraído.
-Fotografia editorial extremamente realista para catálogo premium de joias, produzida como uma campanha de joalheria de luxo. Enquadramento fechado, mostrando apenas o pulso — nunca mostrar rosto, olhos, boca, nariz, cabelo ou outras partes do corpo além das in